--- a/downloads/indicadores/PIB/PIB_datos.xlsx
+++ b/downloads/indicadores/PIB/PIB_datos.xlsx
@@ -2437,7 +2437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6866,7 +6866,7 @@
         <v>46023</v>
       </c>
       <c r="C137" s="10" t="n">
-        <v>24973976.071</v>
+        <v>24963384.137</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
@@ -6884,6 +6884,39 @@
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>737372</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>2T-26</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>26144132.442</v>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Millones de pesos (a precios de 2018)</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
         <is>
           <t>737372</t>
         </is>

--- a/downloads/indicadores/PIB/PIB_datos.xlsx
+++ b/downloads/indicadores/PIB/PIB_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -587,12 +587,12 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -625,12 +625,12 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2375,12 +2375,12 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,54 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>30 de julio de 2026</t>
+          <t>30 de octubre de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>3T-26 P</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibo/pib_eo2026_10.pdf</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>30 de octubre de 2026</t>
         </is>
       </c>
     </row>
